--- a/scripts/typescript/src/pppdb/data/sheets/solvents.xlsx
+++ b/scripts/typescript/src/pppdb/data/sheets/solvents.xlsx
@@ -2143,7 +2143,7 @@
       </c>
     </row>
     <row r="55" ht="21.75" customHeight="1">
-      <c r="G55" s="38"/>
+      <c r="G55" s="37"/>
     </row>
     <row r="56" ht="21.75" customHeight="1">
       <c r="G56" s="38"/>
